--- a/naver-place-crawler/results_health/사상구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/사상구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뉴핏 헬스&amp;PT&amp;필라테스&amp;스피닝 사상점</t>
+          <t>미라클짐 헬스&amp;PT 필라테스 학장점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthstar02@naver.com</t>
+          <t>miraclegym2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1448-0905</t>
+          <t>051-313-7705</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로81번길 30 8~10층 뉴핏 사상점</t>
+          <t>부산 사상구 대동로 95 3층 미라클짐 학장점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newfit_sasang</t>
+          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4iq5a</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>357</v>
+        <v>120</v>
       </c>
       <c r="Q2" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="R2" t="n">
-        <v>599</v>
+        <v>266</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>603428544</t>
+          <t>1169221564</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/603428544</t>
+          <t>https://m.place.naver.com/place/1169221564</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프원피트니스 헬스&amp;PT 냉정점</t>
+          <t>뉴핏 헬스&amp;PT&amp;필라테스&amp;스피닝 사상점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>f1nj0401@naver.com</t>
+          <t>healthstar02@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1440-2371</t>
+          <t>0507-1448-0905</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 374 6층, 7층</t>
+          <t>부산광역시 사상구 광장로81번길 30 8~10층 뉴핏 사상점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f1nj0401</t>
+          <t>https://www.instagram.com/newfit_sasang</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>300</v>
+        <v>357</v>
       </c>
       <c r="Q3" t="n">
-        <v>433</v>
+        <v>243</v>
       </c>
       <c r="R3" t="n">
-        <v>733</v>
+        <v>600</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1871691088</t>
+          <t>603428544</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1871691088</t>
+          <t>https://m.place.naver.com/place/603428544</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q4" t="n">
         <v>587</v>
       </c>
       <c r="R4" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,41 +838,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;pt 사상점</t>
+          <t>에프원피트니스 헬스&amp;PT 냉정점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>404sasang_@naver.com</t>
+          <t>f1nj0401@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1309-4044</t>
+          <t>0507-1440-2371</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 84 하이앤드 4, 5층</t>
+          <t>부산광역시 사상구 가야대로 374 6층, 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/404sasang_</t>
+          <t>https://blog.naver.com/f1nj0401</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>593</v>
+        <v>304</v>
       </c>
       <c r="Q5" t="n">
-        <v>683</v>
+        <v>433</v>
       </c>
       <c r="R5" t="n">
-        <v>1276</v>
+        <v>737</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +922,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1720813988</t>
+          <t>1871691088</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720813988</t>
+          <t>https://m.place.naver.com/place/1871691088</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에프원 피트니스 헬스&amp;PT 모라점</t>
+          <t>404피트니스 헬스&amp;pt 사상점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mora44@naver.com</t>
+          <t>404sasang_@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1328-1146</t>
+          <t>0507-1309-4044</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 524 8층 801호</t>
+          <t>부산 사상구 광장로 84 하이앤드 4, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f1fitness_moraboss/</t>
+          <t>https://blog.naver.com/404sasang_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +981,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wgkn</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>305</v>
+        <v>597</v>
       </c>
       <c r="Q6" t="n">
-        <v>56</v>
+        <v>685</v>
       </c>
       <c r="R6" t="n">
-        <v>361</v>
+        <v>1282</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1178892172</t>
+          <t>1720813988</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178892172</t>
+          <t>https://m.place.naver.com/place/1720813988</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1042,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미라클짐 헬스&amp;PT 필라테스 학장점</t>
+          <t>에프원 피트니스 헬스&amp;PT 모라점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miraclegym2@naver.com</t>
+          <t>mora44@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>051-313-7705</t>
+          <t>0507-1328-1146</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 95 3층 미라클짐 학장점</t>
+          <t>부산광역시 사상구 사상로 524 8층 801호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/f1fitness_moraboss/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>120</v>
+        <v>305</v>
       </c>
       <c r="Q7" t="n">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="R7" t="n">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1169221564</t>
+          <t>1178892172</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169221564</t>
+          <t>https://m.place.naver.com/place/1178892172</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1153,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로 117 5층 불독짐</t>
+          <t>부산 사상구 학감대로 117 5층 불독짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1178,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3gyx56</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1210,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1251,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로123번길 68 AK 빌딩 삼정그린코아 맞은편</t>
+          <t>부산 사상구 학감대로123번길 68 AK 빌딩 삼정그린코아 맞은편</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1276,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sbug</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1282,10 +1298,10 @@
         <v>85</v>
       </c>
       <c r="Q9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R9" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1304,7 +1320,105 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>뉴인핏 PT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>in-fit@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1414-4020</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>부산 사상구 사상로 182 청호빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/749373</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4czxd</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2267</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>38643118</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38643118</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
